--- a/data/trans_orig/IP07_C14_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C14_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han producido situaciones de cyberbulling en su colegio en 2023 (tasa de respuesta: 94,11%)</t>
+          <t>Menores según si se han producido situaciones de cyberbulling en su colegio/instituto en 2023 (tasa de respuesta: 94,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11965</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7122</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18362</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5300</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2581</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9845</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19826</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>17604</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>79523</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>73126</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84366</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>61056</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56511</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>63775</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79574</t>
+          <t>64286</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72378</t>
+          <t>59392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84439</t>
+          <t>67182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>140629</t>
+          <t>143808</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133261</t>
+          <t>136417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146726</t>
+          <t>149679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>91488</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>91488</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>91488</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>66356</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>66356</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>66356</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>92204</t>
+          <t>69924</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92204</t>
+          <t>69924</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92204</t>
+          <t>69924</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>158559</t>
+          <t>161412</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158559</t>
+          <t>161412</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158559</t>
+          <t>161412</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19628</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12130</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>30224</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21249</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10200</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>30192</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,67%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20770</t>
+          <t>21652</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31989</t>
+          <t>29714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42019</t>
+          <t>41280</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28180</t>
+          <t>30858</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55775</t>
+          <t>52898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>137952</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>127356</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>145450</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>114323</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>105380</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>125372</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>137932</t>
+          <t>96934</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126713</t>
+          <t>88872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145640</t>
+          <t>102871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>252255</t>
+          <t>234886</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>238499</t>
+          <t>223268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>266094</t>
+          <t>245308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157580</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157580</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157580</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>135572</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>135572</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>135572</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>158702</t>
+          <t>118586</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>158702</t>
+          <t>118586</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>158702</t>
+          <t>118586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>294274</t>
+          <t>276166</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>294274</t>
+          <t>276166</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>294274</t>
+          <t>276166</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31593</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22255</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42528</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>26548</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16535</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36535</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>21073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>36454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>58883</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>46261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73927</t>
+          <t>72535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>217475</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>206540</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>226813</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>175379</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>165392</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>185392</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>217506</t>
+          <t>161219</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204723</t>
+          <t>152056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>226637</t>
+          <t>167437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>392885</t>
+          <t>378694</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378906</t>
+          <t>365042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>407436</t>
+          <t>391316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
